--- a/GWD Data/GI wo Trench.xlsx
+++ b/GWD Data/GI wo Trench.xlsx
@@ -788,7 +788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50DF0088-2B8F-42B5-A93D-ABC3BA18B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF91D57-6781-4C14-BDB5-BFF592CDB9A6}">
   <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/GI wo Trench.xlsx
+++ b/GWD Data/GI wo Trench.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="50">
   <si>
     <t>GI Pipe Without Trenching</t>
   </si>
@@ -153,6 +153,18 @@
   </si>
   <si>
     <t>1.02 x 86.40 = 88.128 kg = 0.088128 tonne</t>
+  </si>
+  <si>
+    <t>Providing and fixing G.I. pipes complete with G.I fittings: 15 mm dia nominal bore</t>
+  </si>
+  <si>
+    <t>G.I. pipes 15 mm dia</t>
+  </si>
+  <si>
+    <t>Providing and fixing G.I. pipes complete with G.I fittings: 20 mm dia nominal bore</t>
+  </si>
+  <si>
+    <t>G.I. pipes 20 mm dia</t>
   </si>
 </sst>
 </file>
@@ -788,8 +800,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF91D57-6781-4C14-BDB5-BFF592CDB9A6}">
-  <dimension ref="A1:F121"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CF4D3A-2B09-4DF6-8BAD-3654E9F0B9A6}">
+  <dimension ref="A1:F161"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -2548,8 +2560,590 @@
         <v>699</v>
       </c>
     </row>
+    <row r="122" spans="1:6" ht="12.75">
+      <c r="A122" s="6">
+        <v>0</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="3"/>
+    </row>
+    <row r="123" spans="1:6" ht="12.75">
+      <c r="A123" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="12.75">
+      <c r="A124" s="7"/>
+      <c r="B124" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.75">
+      <c r="A125" s="9"/>
+      <c r="B125" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+    </row>
+    <row r="126" spans="1:6" ht="12.75">
+      <c r="A126" s="7">
+        <v>1545</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="7">
+        <v>10.20</v>
+      </c>
+      <c r="E126" s="7">
+        <v>95</v>
+      </c>
+      <c r="F126" s="7">
+        <f>D126*E126</f>
+        <v>969</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="12.75">
+      <c r="A127" s="10"/>
+      <c r="B127" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+    </row>
+    <row r="128" spans="1:6" ht="12.75">
+      <c r="A128" s="9"/>
+      <c r="B128" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+    </row>
+    <row r="129" spans="1:6" ht="12.75">
+      <c r="A129" s="11">
+        <v>2271</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="11">
+        <v>0.067629999999999996</v>
+      </c>
+      <c r="E129" s="11">
+        <v>145.72</v>
+      </c>
+      <c r="F129" s="11">
+        <f>D129*E129</f>
+        <v>9.8550436000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="12.75">
+      <c r="A130" s="7">
+        <v>9999</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" s="7">
+        <v>13.52</v>
+      </c>
+      <c r="E130" s="7">
+        <v>2.12</v>
+      </c>
+      <c r="F130" s="7">
+        <f>D130*E130</f>
+        <v>28.662400000000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="12.75">
+      <c r="A131" s="9"/>
+      <c r="B131" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+    </row>
+    <row r="132" spans="1:6" ht="12.75">
+      <c r="A132" s="11">
+        <v>116</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D132" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="E132" s="11">
+        <v>784</v>
+      </c>
+      <c r="F132" s="11">
+        <f>E132*D132</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="12.75">
+      <c r="A133" s="11">
+        <v>114</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D133" s="11">
+        <v>0.66</v>
+      </c>
+      <c r="E133" s="11">
+        <v>645</v>
+      </c>
+      <c r="F133" s="11">
+        <f>D133*E133</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="12.75">
+      <c r="A134" s="12"/>
+      <c r="B134" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="14">
+        <f>SUM(F126:F133)</f>
+        <v>1629.2174439999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="12.75">
+      <c r="A135" s="10"/>
+      <c r="B135" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="14">
+        <f>F134*0.01</f>
+        <v>16.29217444</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="12.75">
+      <c r="A136" s="10"/>
+      <c r="B136" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="14">
+        <f>SUM(F134:F135)</f>
+        <v>1645.509618</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="12.75">
+      <c r="A137" s="10"/>
+      <c r="B137" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="3"/>
+      <c r="F137" s="14">
+        <f>F136*0.15</f>
+        <v>246.8264427</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="12.75">
+      <c r="A138" s="10"/>
+      <c r="B138" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="14">
+        <f>SUM(F136:F137)</f>
+        <v>1892.336061</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="12.75">
+      <c r="A139" s="10"/>
+      <c r="B139" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="14">
+        <f>F138</f>
+        <v>1892.336061</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="12.75">
+      <c r="A140" s="10"/>
+      <c r="B140" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="14">
+        <f>F139/10</f>
+        <v>189.2336061</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="12.75">
+      <c r="A141" s="9"/>
+      <c r="B141" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="15">
+        <f>MROUND(F140,0.05)</f>
+        <v>189.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="12.75">
+      <c r="A142" s="16">
+        <v>0</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="3"/>
+    </row>
+    <row r="143" spans="1:6" ht="12.75">
+      <c r="A143" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B143" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D143" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E143" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F143" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="12.75">
+      <c r="A144" s="18"/>
+      <c r="B144" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" s="18"/>
+      <c r="D144" s="18"/>
+      <c r="E144" s="18"/>
+      <c r="F144" s="18"/>
+    </row>
+    <row r="145" spans="1:6" ht="12.75">
+      <c r="A145" s="9"/>
+      <c r="B145" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+    </row>
+    <row r="146" spans="1:6" ht="12.75">
+      <c r="A146" s="18">
+        <v>1552</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C146" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="18">
+        <v>10.20</v>
+      </c>
+      <c r="E146" s="18">
+        <v>130</v>
+      </c>
+      <c r="F146" s="18">
+        <f>D146*E146</f>
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="12.75">
+      <c r="A147" s="10"/>
+      <c r="B147" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" s="10"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+    </row>
+    <row r="148" spans="1:6" ht="12.75">
+      <c r="A148" s="9"/>
+      <c r="B148" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C148" s="9"/>
+      <c r="D148" s="9"/>
+      <c r="E148" s="9"/>
+      <c r="F148" s="9"/>
+    </row>
+    <row r="149" spans="1:6" ht="12.75">
+      <c r="A149" s="20">
+        <v>2271</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="20">
+        <v>0.08813</v>
+      </c>
+      <c r="E149" s="20">
+        <v>145.72</v>
+      </c>
+      <c r="F149" s="20">
+        <f>E149*D149</f>
+        <v>12.842303599999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="12.75">
+      <c r="A150" s="18">
+        <v>9999</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="18">
+        <v>13.52</v>
+      </c>
+      <c r="E150" s="18">
+        <v>2.12</v>
+      </c>
+      <c r="F150" s="18">
+        <f>E150*D150</f>
+        <v>28.662400000000002</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="12.75">
+      <c r="A151" s="9"/>
+      <c r="B151" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" s="9"/>
+      <c r="D151" s="9"/>
+      <c r="E151" s="9"/>
+      <c r="F151" s="9"/>
+    </row>
+    <row r="152" spans="1:6" ht="12.75">
+      <c r="A152" s="20">
+        <v>116</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="20">
+        <v>0.25</v>
+      </c>
+      <c r="E152" s="20">
+        <v>784</v>
+      </c>
+      <c r="F152" s="20">
+        <f>E152*D152</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="12.75">
+      <c r="A153" s="20">
+        <v>114</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="20">
+        <v>0.66</v>
+      </c>
+      <c r="E153" s="20">
+        <v>645</v>
+      </c>
+      <c r="F153" s="20">
+        <f>E153*D153</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="12.75">
+      <c r="A154" s="21"/>
+      <c r="B154" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="23">
+        <f>SUM(F146:F153)</f>
+        <v>1989.204704</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="12.75">
+      <c r="A155" s="10"/>
+      <c r="B155" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="23">
+        <f>F154*0.01</f>
+        <v>19.892047040000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="12.75">
+      <c r="A156" s="10"/>
+      <c r="B156" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="23">
+        <f>SUM(F154:F155)</f>
+        <v>2009.096751</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="12.75">
+      <c r="A157" s="10"/>
+      <c r="B157" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="23">
+        <f>F156*0.15</f>
+        <v>301.36451260000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="12.75">
+      <c r="A158" s="10"/>
+      <c r="B158" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="23">
+        <f>SUM(F156:F157)</f>
+        <v>2310.4612630000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="12.75">
+      <c r="A159" s="10"/>
+      <c r="B159" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="23">
+        <f>F158</f>
+        <v>2310.4612630000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="12.75">
+      <c r="A160" s="10"/>
+      <c r="B160" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="23">
+        <f>F159/10</f>
+        <v>231.0461263</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="12.75">
+      <c r="A161" s="9"/>
+      <c r="B161" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="25">
+        <f>MROUND(F160,0.05)</f>
+        <v>231.05</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="149">
+  <mergeCells count="199">
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A21"/>
@@ -2564,8 +3158,6 @@
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A114:A121"/>
     <mergeCell ref="A74:A81"/>
     <mergeCell ref="A84:A85"/>
     <mergeCell ref="A86:A88"/>
@@ -2573,6 +3165,16 @@
     <mergeCell ref="A94:A101"/>
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="A106:A108"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A154:A161"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A114:A121"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A128"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A134:A141"/>
+    <mergeCell ref="A144:A145"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C10:C11"/>
@@ -2580,10 +3182,6 @@
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="C110:C111"/>
     <mergeCell ref="C46:C48"/>
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="C64:C65"/>
@@ -2591,6 +3189,16 @@
     <mergeCell ref="C70:C71"/>
     <mergeCell ref="C84:C85"/>
     <mergeCell ref="C86:C88"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="C146:C148"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="C110:C111"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="C126:C128"/>
+    <mergeCell ref="C130:C131"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A4:A5"/>
@@ -2640,9 +3248,6 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B121:E121"/>
     <mergeCell ref="E110:E111"/>
     <mergeCell ref="F110:F111"/>
     <mergeCell ref="B114:E114"/>
@@ -2650,6 +3255,45 @@
     <mergeCell ref="B116:E116"/>
     <mergeCell ref="B117:E117"/>
     <mergeCell ref="B118:E118"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="D126:D128"/>
+    <mergeCell ref="E126:E128"/>
+    <mergeCell ref="F126:F128"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:F131"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B136:E136"/>
+    <mergeCell ref="B137:E137"/>
+    <mergeCell ref="B138:E138"/>
+    <mergeCell ref="B139:E139"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="E144:E145"/>
+    <mergeCell ref="F144:F145"/>
+    <mergeCell ref="D146:D148"/>
+    <mergeCell ref="E146:E148"/>
+    <mergeCell ref="F146:F148"/>
+    <mergeCell ref="B158:E158"/>
+    <mergeCell ref="B159:E159"/>
+    <mergeCell ref="B160:E160"/>
+    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="B154:E154"/>
+    <mergeCell ref="B155:E155"/>
+    <mergeCell ref="B156:E156"/>
+    <mergeCell ref="B157:E157"/>
     <mergeCell ref="B57:E57"/>
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B59:E59"/>
